--- a/gstdatabase/GSTR-1-2018-2019.xlsx
+++ b/gstdatabase/GSTR-1-2018-2019.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Aug-26\GST Statistics Downloads 31st Aug 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85820234-A21C-4390-8FAC-FEBF03B04F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E0D4FF-6613-45B3-9B4E-90D45F7A4517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -185,10 +185,10 @@
     <t>-</t>
   </si>
   <si>
-    <t>Data Considered upto 31st Jul 2026</t>
+    <t>Data Considered upto 31st Aug 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st Jul 2026</t>
+    <t>Filing %age as on 31st Aug 2026</t>
   </si>
 </sst>
 </file>
@@ -1364,14 +1364,14 @@
       </c>
       <c r="AD11" s="11">
         <f t="shared" ref="AD11:AD48" si="10">AE11-AC11</f>
-        <v>30891</v>
+        <v>30892</v>
       </c>
       <c r="AE11" s="6">
-        <v>70404</v>
+        <v>70405</v>
       </c>
       <c r="AF11" s="12">
         <f t="shared" ref="AF11:AF48" si="11">AE11/AB11</f>
-        <v>0.89040091058555715</v>
+        <v>0.89041355760718355</v>
       </c>
       <c r="AG11" s="5">
         <v>30015</v>
@@ -1415,14 +1415,14 @@
       </c>
       <c r="AS11" s="11">
         <f t="shared" ref="AS11:AS48" si="16">AT11-AR11</f>
-        <v>59992</v>
+        <v>59993</v>
       </c>
       <c r="AT11" s="6">
-        <v>73144</v>
+        <v>73145</v>
       </c>
       <c r="AU11" s="12">
         <f t="shared" ref="AU11:AU48" si="17">AT11/AQ11</f>
-        <v>0.88444981862152361</v>
+        <v>0.8844619105199516</v>
       </c>
       <c r="AV11" s="5">
         <v>29226</v>
@@ -1466,14 +1466,14 @@
       </c>
       <c r="BH11" s="11">
         <f t="shared" ref="BH11:BH48" si="22">BI11-BG11</f>
-        <v>63180</v>
+        <v>63181</v>
       </c>
       <c r="BI11" s="6">
-        <v>75338</v>
+        <v>75339</v>
       </c>
       <c r="BJ11" s="12">
         <f t="shared" ref="BJ11:BJ48" si="23">BI11/BF11</f>
-        <v>0.86929130224078643</v>
+        <v>0.869302840791083</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1627,14 +1627,14 @@
       </c>
       <c r="AS12" s="11">
         <f t="shared" si="16"/>
-        <v>203705</v>
+        <v>203706</v>
       </c>
       <c r="AT12" s="6">
-        <v>272707</v>
+        <v>272708</v>
       </c>
       <c r="AU12" s="12">
         <f t="shared" si="17"/>
-        <v>0.92513298233234731</v>
+        <v>0.92513637473878474</v>
       </c>
       <c r="AV12" s="5">
         <v>96791</v>
@@ -1678,14 +1678,14 @@
       </c>
       <c r="BH12" s="11">
         <f t="shared" si="22"/>
-        <v>218710</v>
+        <v>218711</v>
       </c>
       <c r="BI12" s="6">
-        <v>276499</v>
+        <v>276500</v>
       </c>
       <c r="BJ12" s="12">
         <f t="shared" si="23"/>
-        <v>0.91319195595525504</v>
+        <v>0.91319525865058471</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -1915,14 +1915,14 @@
       </c>
       <c r="E14" s="11">
         <f t="shared" si="0"/>
-        <v>5961</v>
+        <v>5963</v>
       </c>
       <c r="F14" s="6">
-        <v>28302</v>
+        <v>28304</v>
       </c>
       <c r="G14" s="12">
         <f t="shared" si="1"/>
-        <v>0.54052711993888469</v>
+        <v>0.54056531703590527</v>
       </c>
       <c r="H14" s="5">
         <v>53901</v>
@@ -1932,14 +1932,14 @@
       </c>
       <c r="J14" s="11">
         <f t="shared" si="2"/>
-        <v>6568</v>
+        <v>6570</v>
       </c>
       <c r="K14" s="6">
-        <v>28617</v>
+        <v>28619</v>
       </c>
       <c r="L14" s="12">
         <f t="shared" si="3"/>
-        <v>0.53091779373295489</v>
+        <v>0.53095489879594071</v>
       </c>
       <c r="M14" s="5">
         <v>118806</v>
@@ -1949,14 +1949,14 @@
       </c>
       <c r="O14" s="11">
         <f t="shared" si="4"/>
-        <v>35306</v>
+        <v>35311</v>
       </c>
       <c r="P14" s="6">
-        <v>98342</v>
+        <v>98347</v>
       </c>
       <c r="Q14" s="12">
         <f t="shared" si="5"/>
-        <v>0.8277528070972846</v>
+        <v>0.82779489251384608</v>
       </c>
       <c r="R14" s="5">
         <v>54910</v>
@@ -1966,14 +1966,14 @@
       </c>
       <c r="T14" s="11">
         <f t="shared" si="6"/>
-        <v>8470</v>
+        <v>8472</v>
       </c>
       <c r="U14" s="6">
-        <v>29180</v>
+        <v>29182</v>
       </c>
       <c r="V14" s="12">
         <f t="shared" si="7"/>
-        <v>0.53141504279730467</v>
+        <v>0.53145146603533056</v>
       </c>
       <c r="W14" s="5">
         <v>53463</v>
@@ -1983,14 +1983,14 @@
       </c>
       <c r="Y14" s="11">
         <f t="shared" si="8"/>
-        <v>10196</v>
+        <v>10199</v>
       </c>
       <c r="Z14" s="6">
-        <v>29324</v>
+        <v>29327</v>
       </c>
       <c r="AA14" s="12">
         <f t="shared" si="9"/>
-        <v>0.54849148008903359</v>
+        <v>0.54854759366290706</v>
       </c>
       <c r="AB14" s="5">
         <v>122477</v>
@@ -2000,14 +2000,14 @@
       </c>
       <c r="AD14" s="11">
         <f t="shared" si="10"/>
-        <v>55166</v>
+        <v>55170</v>
       </c>
       <c r="AE14" s="6">
-        <v>102366</v>
+        <v>102370</v>
       </c>
       <c r="AF14" s="12">
         <f t="shared" si="11"/>
-        <v>0.83579774161679332</v>
+        <v>0.83583040080994797</v>
       </c>
       <c r="AG14" s="5">
         <v>49944</v>
@@ -2017,14 +2017,14 @@
       </c>
       <c r="AI14" s="11">
         <f t="shared" si="12"/>
-        <v>22755</v>
+        <v>22757</v>
       </c>
       <c r="AJ14" s="6">
-        <v>29760</v>
+        <v>29762</v>
       </c>
       <c r="AK14" s="12">
         <f t="shared" si="13"/>
-        <v>0.59586737145603075</v>
+        <v>0.59590741630626298</v>
       </c>
       <c r="AL14" s="5">
         <v>48590</v>
@@ -2034,14 +2034,14 @@
       </c>
       <c r="AN14" s="11">
         <f t="shared" si="14"/>
-        <v>19978</v>
+        <v>19981</v>
       </c>
       <c r="AO14" s="6">
-        <v>29774</v>
+        <v>29777</v>
       </c>
       <c r="AP14" s="12">
         <f t="shared" si="15"/>
-        <v>0.61275982712492283</v>
+        <v>0.61282156822391443</v>
       </c>
       <c r="AQ14" s="5">
         <v>123658</v>
@@ -2051,14 +2051,14 @@
       </c>
       <c r="AS14" s="11">
         <f t="shared" si="16"/>
-        <v>87221</v>
+        <v>87225</v>
       </c>
       <c r="AT14" s="6">
-        <v>105111</v>
+        <v>105115</v>
       </c>
       <c r="AU14" s="12">
         <f t="shared" si="17"/>
-        <v>0.85001374759417103</v>
+        <v>0.85004609487457339</v>
       </c>
       <c r="AV14" s="5">
         <v>44859</v>
@@ -2068,14 +2068,14 @@
       </c>
       <c r="AX14" s="11">
         <f t="shared" si="18"/>
-        <v>19904</v>
+        <v>19906</v>
       </c>
       <c r="AY14" s="6">
-        <v>30197</v>
+        <v>30199</v>
       </c>
       <c r="AZ14" s="12">
         <f t="shared" si="19"/>
-        <v>0.67315365924340709</v>
+        <v>0.67319824338482803</v>
       </c>
       <c r="BA14" s="5">
         <v>44209</v>
@@ -2085,14 +2085,14 @@
       </c>
       <c r="BC14" s="11">
         <f t="shared" si="20"/>
-        <v>19910</v>
+        <v>19913</v>
       </c>
       <c r="BD14" s="6">
-        <v>30167</v>
+        <v>30170</v>
       </c>
       <c r="BE14" s="12">
         <f t="shared" si="21"/>
-        <v>0.68237236761745346</v>
+        <v>0.68244022710307861</v>
       </c>
       <c r="BF14" s="5">
         <v>128280</v>
@@ -2102,14 +2102,14 @@
       </c>
       <c r="BH14" s="11">
         <f t="shared" si="22"/>
-        <v>92378</v>
+        <v>92382</v>
       </c>
       <c r="BI14" s="6">
-        <v>108329</v>
+        <v>108333</v>
       </c>
       <c r="BJ14" s="12">
         <f t="shared" si="23"/>
-        <v>0.844473027751793</v>
+        <v>0.84450420954162764</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2263,14 +2263,14 @@
       </c>
       <c r="AS15" s="11">
         <f t="shared" si="16"/>
-        <v>279483</v>
+        <v>279484</v>
       </c>
       <c r="AT15" s="6">
-        <v>362521</v>
+        <v>362522</v>
       </c>
       <c r="AU15" s="12">
         <f t="shared" si="17"/>
-        <v>0.86976581262610875</v>
+        <v>0.86976821184108555</v>
       </c>
       <c r="AV15" s="5">
         <v>155966</v>
@@ -2314,14 +2314,14 @@
       </c>
       <c r="BH15" s="11">
         <f t="shared" si="22"/>
-        <v>294443</v>
+        <v>294444</v>
       </c>
       <c r="BI15" s="6">
-        <v>367693</v>
+        <v>367694</v>
       </c>
       <c r="BJ15" s="12">
         <f t="shared" si="23"/>
-        <v>0.87239368315159105</v>
+        <v>0.87239605576592738</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2339,14 +2339,14 @@
       </c>
       <c r="E16" s="11">
         <f t="shared" si="0"/>
-        <v>20429</v>
+        <v>20430</v>
       </c>
       <c r="F16" s="6">
-        <v>152509</v>
+        <v>152510</v>
       </c>
       <c r="G16" s="12">
         <f t="shared" si="1"/>
-        <v>0.5960106767546105</v>
+        <v>0.59601458479070513</v>
       </c>
       <c r="H16" s="5">
         <v>262865</v>
@@ -2356,14 +2356,14 @@
       </c>
       <c r="J16" s="11">
         <f t="shared" si="2"/>
-        <v>22462</v>
+        <v>22463</v>
       </c>
       <c r="K16" s="6">
-        <v>154151</v>
+        <v>154152</v>
       </c>
       <c r="L16" s="12">
         <f t="shared" si="3"/>
-        <v>0.58642649268635993</v>
+        <v>0.58643029692047244</v>
       </c>
       <c r="M16" s="5">
         <v>653936</v>
@@ -2390,14 +2390,14 @@
       </c>
       <c r="T16" s="11">
         <f t="shared" si="6"/>
-        <v>32001</v>
+        <v>32002</v>
       </c>
       <c r="U16" s="6">
-        <v>156955</v>
+        <v>156956</v>
       </c>
       <c r="V16" s="12">
         <f t="shared" si="7"/>
-        <v>0.5827565978049396</v>
+        <v>0.58276031069460743</v>
       </c>
       <c r="W16" s="5">
         <v>268583</v>
@@ -2407,14 +2407,14 @@
       </c>
       <c r="Y16" s="11">
         <f t="shared" si="8"/>
-        <v>44538</v>
+        <v>44539</v>
       </c>
       <c r="Z16" s="6">
-        <v>158065</v>
+        <v>158066</v>
       </c>
       <c r="AA16" s="12">
         <f t="shared" si="9"/>
-        <v>0.58851453740556925</v>
+        <v>0.58851826064940815</v>
       </c>
       <c r="AB16" s="5">
         <v>674957</v>
@@ -2441,14 +2441,14 @@
       </c>
       <c r="AI16" s="11">
         <f t="shared" si="12"/>
-        <v>108747</v>
+        <v>108748</v>
       </c>
       <c r="AJ16" s="6">
-        <v>160362</v>
+        <v>160363</v>
       </c>
       <c r="AK16" s="12">
         <f t="shared" si="13"/>
-        <v>0.62673477443535563</v>
+        <v>0.62673868268528032</v>
       </c>
       <c r="AL16" s="5">
         <v>254489</v>
@@ -2458,14 +2458,14 @@
       </c>
       <c r="AN16" s="11">
         <f t="shared" si="14"/>
-        <v>86202</v>
+        <v>86203</v>
       </c>
       <c r="AO16" s="6">
-        <v>160883</v>
+        <v>160884</v>
       </c>
       <c r="AP16" s="12">
         <f t="shared" si="15"/>
-        <v>0.63218056576119208</v>
+        <v>0.6321844952041149</v>
       </c>
       <c r="AQ16" s="5">
         <v>700345</v>
@@ -2492,14 +2492,14 @@
       </c>
       <c r="AX16" s="11">
         <f t="shared" si="18"/>
-        <v>83271</v>
+        <v>83272</v>
       </c>
       <c r="AY16" s="6">
-        <v>162687</v>
+        <v>162688</v>
       </c>
       <c r="AZ16" s="12">
         <f t="shared" si="19"/>
-        <v>0.64433812433907489</v>
+        <v>0.64434208493902656</v>
       </c>
       <c r="BA16" s="5">
         <v>250214</v>
@@ -2509,14 +2509,14 @@
       </c>
       <c r="BC16" s="11">
         <f t="shared" si="20"/>
-        <v>85039</v>
+        <v>85040</v>
       </c>
       <c r="BD16" s="6">
-        <v>163180</v>
+        <v>163181</v>
       </c>
       <c r="BE16" s="12">
         <f t="shared" si="21"/>
-        <v>0.6521617495423917</v>
+        <v>0.65216574612132017</v>
       </c>
       <c r="BF16" s="5">
         <v>730364</v>
@@ -2585,14 +2585,14 @@
       </c>
       <c r="O17" s="11">
         <f t="shared" si="4"/>
-        <v>111631</v>
+        <v>111635</v>
       </c>
       <c r="P17" s="6">
-        <v>448820</v>
+        <v>448824</v>
       </c>
       <c r="Q17" s="12">
         <f t="shared" si="5"/>
-        <v>0.89689199207860648</v>
+        <v>0.8968999854121662</v>
       </c>
       <c r="R17" s="5">
         <v>195360</v>
@@ -2636,14 +2636,14 @@
       </c>
       <c r="AD17" s="11">
         <f t="shared" si="10"/>
-        <v>217807</v>
+        <v>217809</v>
       </c>
       <c r="AE17" s="6">
-        <v>464515</v>
+        <v>464517</v>
       </c>
       <c r="AF17" s="12">
         <f t="shared" si="11"/>
-        <v>0.90825636052213765</v>
+        <v>0.9082602710798614</v>
       </c>
       <c r="AG17" s="5">
         <v>180725</v>
@@ -2687,14 +2687,14 @@
       </c>
       <c r="AS17" s="11">
         <f t="shared" si="16"/>
-        <v>374716</v>
+        <v>374718</v>
       </c>
       <c r="AT17" s="6">
-        <v>475242</v>
+        <v>475244</v>
       </c>
       <c r="AU17" s="12">
         <f t="shared" si="17"/>
-        <v>0.89567918219957254</v>
+        <v>0.89568295155994981</v>
       </c>
       <c r="AV17" s="5">
         <v>171569</v>
@@ -2738,14 +2738,14 @@
       </c>
       <c r="BH17" s="11">
         <f t="shared" si="22"/>
-        <v>407042</v>
+        <v>407043</v>
       </c>
       <c r="BI17" s="6">
-        <v>486582</v>
+        <v>486583</v>
       </c>
       <c r="BJ17" s="12">
         <f t="shared" si="23"/>
-        <v>0.88239710426670925</v>
+        <v>0.88239891772693646</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2848,14 +2848,14 @@
       </c>
       <c r="AD18" s="11">
         <f t="shared" si="10"/>
-        <v>436543</v>
+        <v>436544</v>
       </c>
       <c r="AE18" s="6">
-        <v>905338</v>
+        <v>905339</v>
       </c>
       <c r="AF18" s="12">
         <f t="shared" si="11"/>
-        <v>0.86148988769604662</v>
+        <v>0.86149083926318248</v>
       </c>
       <c r="AG18" s="5">
         <v>403018</v>
@@ -2899,14 +2899,14 @@
       </c>
       <c r="AS18" s="11">
         <f t="shared" si="16"/>
-        <v>781421</v>
+        <v>781423</v>
       </c>
       <c r="AT18" s="6">
-        <v>931167</v>
+        <v>931169</v>
       </c>
       <c r="AU18" s="12">
         <f t="shared" si="17"/>
-        <v>0.86141400124887257</v>
+        <v>0.86141585143042165</v>
       </c>
       <c r="AV18" s="5">
         <v>383854</v>
@@ -2950,14 +2950,14 @@
       </c>
       <c r="BH18" s="11">
         <f t="shared" si="22"/>
-        <v>810037</v>
+        <v>810038</v>
       </c>
       <c r="BI18" s="6">
-        <v>946550</v>
+        <v>946551</v>
       </c>
       <c r="BJ18" s="12">
         <f t="shared" si="23"/>
-        <v>0.85394943154240477</v>
+        <v>0.85395033371284634</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -4493,14 +4493,14 @@
       </c>
       <c r="O26" s="11">
         <f t="shared" si="4"/>
-        <v>6003</v>
+        <v>6004</v>
       </c>
       <c r="P26" s="6">
-        <v>15207</v>
+        <v>15208</v>
       </c>
       <c r="Q26" s="12">
         <f t="shared" si="5"/>
-        <v>0.75222595963593197</v>
+        <v>0.75227542540561931</v>
       </c>
       <c r="R26" s="5">
         <v>13942</v>
@@ -4510,14 +4510,14 @@
       </c>
       <c r="T26" s="11">
         <f t="shared" si="6"/>
-        <v>3185</v>
+        <v>3187</v>
       </c>
       <c r="U26" s="6">
-        <v>7344</v>
+        <v>7346</v>
       </c>
       <c r="V26" s="12">
         <f t="shared" si="7"/>
-        <v>0.52675369387462345</v>
+        <v>0.52689714531631038</v>
       </c>
       <c r="W26" s="5">
         <v>13671</v>
@@ -4527,14 +4527,14 @@
       </c>
       <c r="Y26" s="11">
         <f t="shared" si="8"/>
-        <v>3681</v>
+        <v>3683</v>
       </c>
       <c r="Z26" s="6">
-        <v>7482</v>
+        <v>7484</v>
       </c>
       <c r="AA26" s="12">
         <f t="shared" si="9"/>
-        <v>0.54728988369541365</v>
+        <v>0.54743617877258433</v>
       </c>
       <c r="AB26" s="5">
         <v>22408</v>
@@ -4544,14 +4544,14 @@
       </c>
       <c r="AD26" s="11">
         <f t="shared" si="10"/>
-        <v>8967</v>
+        <v>8968</v>
       </c>
       <c r="AE26" s="6">
-        <v>16712</v>
+        <v>16713</v>
       </c>
       <c r="AF26" s="12">
         <f t="shared" si="11"/>
-        <v>0.74580506961799353</v>
+        <v>0.7458496965369511</v>
       </c>
       <c r="AG26" s="5">
         <v>13544</v>
@@ -4561,14 +4561,14 @@
       </c>
       <c r="AI26" s="11">
         <f t="shared" si="12"/>
-        <v>6358</v>
+        <v>6360</v>
       </c>
       <c r="AJ26" s="6">
-        <v>7612</v>
+        <v>7614</v>
       </c>
       <c r="AK26" s="12">
         <f t="shared" si="13"/>
-        <v>0.56202008269344361</v>
+        <v>0.56216774955699944</v>
       </c>
       <c r="AL26" s="5">
         <v>13664</v>
@@ -4578,14 +4578,14 @@
       </c>
       <c r="AN26" s="11">
         <f t="shared" si="14"/>
-        <v>6172</v>
+        <v>6174</v>
       </c>
       <c r="AO26" s="6">
-        <v>7606</v>
+        <v>7608</v>
       </c>
       <c r="AP26" s="12">
         <f t="shared" si="15"/>
-        <v>0.55664519906323184</v>
+        <v>0.55679156908665106</v>
       </c>
       <c r="AQ26" s="5">
         <v>23182</v>
@@ -4595,14 +4595,14 @@
       </c>
       <c r="AS26" s="11">
         <f t="shared" si="16"/>
-        <v>14319</v>
+        <v>14321</v>
       </c>
       <c r="AT26" s="6">
-        <v>16814</v>
+        <v>16816</v>
       </c>
       <c r="AU26" s="12">
         <f t="shared" si="17"/>
-        <v>0.72530411526184113</v>
+        <v>0.72539038909498754</v>
       </c>
       <c r="AV26" s="5">
         <v>13582</v>
@@ -4612,14 +4612,14 @@
       </c>
       <c r="AX26" s="11">
         <f t="shared" si="18"/>
-        <v>6376</v>
+        <v>6378</v>
       </c>
       <c r="AY26" s="6">
-        <v>7671</v>
+        <v>7673</v>
       </c>
       <c r="AZ26" s="12">
         <f t="shared" si="19"/>
-        <v>0.56479163598880877</v>
+        <v>0.56493888970696515</v>
       </c>
       <c r="BA26" s="5">
         <v>13478</v>
@@ -4629,14 +4629,14 @@
       </c>
       <c r="BC26" s="11">
         <f t="shared" si="20"/>
-        <v>6137</v>
+        <v>6139</v>
       </c>
       <c r="BD26" s="6">
-        <v>7646</v>
+        <v>7648</v>
       </c>
       <c r="BE26" s="12">
         <f t="shared" si="21"/>
-        <v>0.56729485086808129</v>
+        <v>0.56744324083691944</v>
       </c>
       <c r="BF26" s="5">
         <v>23703</v>
@@ -4646,14 +4646,14 @@
       </c>
       <c r="BH26" s="11">
         <f t="shared" si="22"/>
-        <v>14216</v>
+        <v>14219</v>
       </c>
       <c r="BI26" s="6">
-        <v>16860</v>
+        <v>16863</v>
       </c>
       <c r="BJ26" s="12">
         <f t="shared" si="23"/>
-        <v>0.71130236678901404</v>
+        <v>0.71142893304644983</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4841,14 +4841,14 @@
       </c>
       <c r="BC27" s="11">
         <f t="shared" si="20"/>
-        <v>36465</v>
+        <v>36467</v>
       </c>
       <c r="BD27" s="6">
-        <v>46868</v>
+        <v>46870</v>
       </c>
       <c r="BE27" s="12">
         <f t="shared" si="21"/>
-        <v>0.54856152999836139</v>
+        <v>0.54858493878602033</v>
       </c>
       <c r="BF27" s="5">
         <v>157244</v>
@@ -4858,14 +4858,14 @@
       </c>
       <c r="BH27" s="11">
         <f t="shared" si="22"/>
-        <v>99078</v>
+        <v>99080</v>
       </c>
       <c r="BI27" s="6">
-        <v>112446</v>
+        <v>112448</v>
       </c>
       <c r="BJ27" s="12">
         <f t="shared" si="23"/>
-        <v>0.71510518684337721</v>
+        <v>0.71511790592963798</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -4917,14 +4917,14 @@
       </c>
       <c r="O28" s="11">
         <f t="shared" si="4"/>
-        <v>123077</v>
+        <v>123078</v>
       </c>
       <c r="P28" s="6">
-        <v>452706</v>
+        <v>452707</v>
       </c>
       <c r="Q28" s="12">
         <f t="shared" si="5"/>
-        <v>0.88505225786018427</v>
+        <v>0.88505421288675312</v>
       </c>
       <c r="R28" s="5">
         <v>239310</v>
@@ -4968,14 +4968,14 @@
       </c>
       <c r="AD28" s="11">
         <f t="shared" si="10"/>
-        <v>216574</v>
+        <v>216575</v>
       </c>
       <c r="AE28" s="6">
-        <v>472347</v>
+        <v>472348</v>
       </c>
       <c r="AF28" s="12">
         <f t="shared" si="11"/>
-        <v>0.88124111477195977</v>
+        <v>0.88124298043664018</v>
       </c>
       <c r="AG28" s="5">
         <v>231591</v>
@@ -5129,14 +5129,14 @@
       </c>
       <c r="O29" s="11">
         <f t="shared" si="4"/>
-        <v>37093</v>
+        <v>37094</v>
       </c>
       <c r="P29" s="6">
-        <v>109708</v>
+        <v>109709</v>
       </c>
       <c r="Q29" s="12">
         <f t="shared" si="5"/>
-        <v>0.86240291796371416</v>
+        <v>0.86241077885734052</v>
       </c>
       <c r="R29" s="5">
         <v>67228</v>
@@ -5282,14 +5282,14 @@
       </c>
       <c r="BH29" s="11">
         <f t="shared" si="22"/>
-        <v>104778</v>
+        <v>104780</v>
       </c>
       <c r="BI29" s="6">
-        <v>121525</v>
+        <v>121527</v>
       </c>
       <c r="BJ29" s="12">
         <f t="shared" si="23"/>
-        <v>0.83199830211414172</v>
+        <v>0.83201199474203091</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5307,14 +5307,14 @@
       </c>
       <c r="E30" s="11">
         <f t="shared" si="0"/>
-        <v>14591</v>
+        <v>14592</v>
       </c>
       <c r="F30" s="6">
-        <v>53378</v>
+        <v>53379</v>
       </c>
       <c r="G30" s="12">
         <f t="shared" si="1"/>
-        <v>0.56278005630120087</v>
+        <v>0.56279059959724609</v>
       </c>
       <c r="H30" s="5">
         <v>100711</v>
@@ -5324,14 +5324,14 @@
       </c>
       <c r="J30" s="11">
         <f t="shared" si="2"/>
-        <v>15761</v>
+        <v>15762</v>
       </c>
       <c r="K30" s="6">
-        <v>54315</v>
+        <v>54316</v>
       </c>
       <c r="L30" s="12">
         <f t="shared" si="3"/>
-        <v>0.53931546702942079</v>
+        <v>0.53932539643137289</v>
       </c>
       <c r="M30" s="5">
         <v>200801</v>
@@ -5358,14 +5358,14 @@
       </c>
       <c r="T30" s="11">
         <f t="shared" si="6"/>
-        <v>19553</v>
+        <v>19554</v>
       </c>
       <c r="U30" s="6">
-        <v>55994</v>
+        <v>55995</v>
       </c>
       <c r="V30" s="12">
         <f t="shared" si="7"/>
-        <v>0.53631531056941717</v>
+        <v>0.53632488865475791</v>
       </c>
       <c r="W30" s="5">
         <v>103393</v>
@@ -5375,14 +5375,14 @@
       </c>
       <c r="Y30" s="11">
         <f t="shared" si="8"/>
-        <v>23197</v>
+        <v>23198</v>
       </c>
       <c r="Z30" s="6">
-        <v>56650</v>
+        <v>56651</v>
       </c>
       <c r="AA30" s="12">
         <f t="shared" si="9"/>
-        <v>0.54790943294033445</v>
+        <v>0.54791910477498473</v>
       </c>
       <c r="AB30" s="5">
         <v>214949</v>
@@ -5409,14 +5409,14 @@
       </c>
       <c r="AI30" s="11">
         <f t="shared" si="12"/>
-        <v>44356</v>
+        <v>44357</v>
       </c>
       <c r="AJ30" s="6">
-        <v>57989</v>
+        <v>57990</v>
       </c>
       <c r="AK30" s="12">
         <f t="shared" si="13"/>
-        <v>0.5659727305556369</v>
+        <v>0.56598249055719851</v>
       </c>
       <c r="AL30" s="5">
         <v>101956</v>
@@ -5426,14 +5426,14 @@
       </c>
       <c r="AN30" s="11">
         <f t="shared" si="14"/>
-        <v>42726</v>
+        <v>42727</v>
       </c>
       <c r="AO30" s="6">
-        <v>58395</v>
+        <v>58396</v>
       </c>
       <c r="AP30" s="12">
         <f t="shared" si="15"/>
-        <v>0.57274706736239167</v>
+        <v>0.57275687551492804</v>
       </c>
       <c r="AQ30" s="5">
         <v>223141</v>
@@ -5460,14 +5460,14 @@
       </c>
       <c r="AX30" s="11">
         <f t="shared" si="18"/>
-        <v>44047</v>
+        <v>44049</v>
       </c>
       <c r="AY30" s="6">
-        <v>59894</v>
+        <v>59896</v>
       </c>
       <c r="AZ30" s="12">
         <f t="shared" si="19"/>
-        <v>0.65571868054871307</v>
+        <v>0.65574057652094897</v>
       </c>
       <c r="BA30" s="5">
         <v>85107</v>
@@ -5477,14 +5477,14 @@
       </c>
       <c r="BC30" s="11">
         <f t="shared" si="20"/>
-        <v>44791</v>
+        <v>44793</v>
       </c>
       <c r="BD30" s="6">
-        <v>60068</v>
+        <v>60070</v>
       </c>
       <c r="BE30" s="12">
         <f t="shared" si="21"/>
-        <v>0.70579388299434831</v>
+        <v>0.70581738282397455</v>
       </c>
       <c r="BF30" s="5">
         <v>218115</v>
@@ -5494,14 +5494,14 @@
       </c>
       <c r="BH30" s="11">
         <f t="shared" si="22"/>
-        <v>155294</v>
+        <v>155295</v>
       </c>
       <c r="BI30" s="6">
-        <v>180144</v>
+        <v>180145</v>
       </c>
       <c r="BJ30" s="12">
         <f t="shared" si="23"/>
-        <v>0.82591293583659997</v>
+        <v>0.82591752057400913</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5553,14 +5553,14 @@
       </c>
       <c r="O31" s="11">
         <f t="shared" si="4"/>
-        <v>34890</v>
+        <v>34891</v>
       </c>
       <c r="P31" s="6">
-        <v>85288</v>
+        <v>85289</v>
       </c>
       <c r="Q31" s="12">
         <f t="shared" si="5"/>
-        <v>0.86777094949330513</v>
+        <v>0.86778112408937369</v>
       </c>
       <c r="R31" s="5">
         <v>50949</v>
@@ -5765,14 +5765,14 @@
       </c>
       <c r="O32" s="11">
         <f t="shared" si="4"/>
-        <v>92603</v>
+        <v>92604</v>
       </c>
       <c r="P32" s="6">
-        <v>287434</v>
+        <v>287435</v>
       </c>
       <c r="Q32" s="12">
         <f t="shared" si="5"/>
-        <v>0.89208700078211323</v>
+        <v>0.89209010440590431</v>
       </c>
       <c r="R32" s="5">
         <v>141043</v>
@@ -5816,14 +5816,14 @@
       </c>
       <c r="AD32" s="11">
         <f t="shared" si="10"/>
-        <v>164670</v>
+        <v>164672</v>
       </c>
       <c r="AE32" s="6">
-        <v>297965</v>
+        <v>297967</v>
       </c>
       <c r="AF32" s="12">
         <f t="shared" si="11"/>
-        <v>0.90581736820025172</v>
+        <v>0.90582344822554461</v>
       </c>
       <c r="AG32" s="5">
         <v>131546</v>
@@ -5867,14 +5867,14 @@
       </c>
       <c r="AS32" s="11">
         <f t="shared" si="16"/>
-        <v>253842</v>
+        <v>253843</v>
       </c>
       <c r="AT32" s="6">
-        <v>306062</v>
+        <v>306063</v>
       </c>
       <c r="AU32" s="12">
         <f t="shared" si="17"/>
-        <v>0.91158521148364691</v>
+        <v>0.91158818991681234</v>
       </c>
       <c r="AV32" s="5">
         <v>125246</v>
@@ -5918,14 +5918,14 @@
       </c>
       <c r="BH32" s="11">
         <f t="shared" si="22"/>
-        <v>274371</v>
+        <v>274372</v>
       </c>
       <c r="BI32" s="6">
-        <v>312743</v>
+        <v>312744</v>
       </c>
       <c r="BJ32" s="12">
         <f t="shared" si="23"/>
-        <v>0.9019732819584001</v>
+        <v>0.90197616603024811</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -5943,14 +5943,14 @@
       </c>
       <c r="E33" s="11">
         <f t="shared" si="0"/>
-        <v>22120</v>
+        <v>22123</v>
       </c>
       <c r="F33" s="6">
-        <v>227293</v>
+        <v>227296</v>
       </c>
       <c r="G33" s="12">
         <f t="shared" si="1"/>
-        <v>0.72393683432706513</v>
+        <v>0.72394638944096212</v>
       </c>
       <c r="H33" s="5">
         <v>329706</v>
@@ -5960,14 +5960,14 @@
       </c>
       <c r="J33" s="11">
         <f t="shared" si="2"/>
-        <v>23708</v>
+        <v>23711</v>
       </c>
       <c r="K33" s="6">
-        <v>229006</v>
+        <v>229009</v>
       </c>
       <c r="L33" s="12">
         <f t="shared" si="3"/>
-        <v>0.69457638016899903</v>
+        <v>0.69458547918448554</v>
       </c>
       <c r="M33" s="5">
         <v>801034</v>
@@ -5977,14 +5977,14 @@
       </c>
       <c r="O33" s="11">
         <f t="shared" si="4"/>
-        <v>145330</v>
+        <v>145332</v>
       </c>
       <c r="P33" s="6">
-        <v>736141</v>
+        <v>736143</v>
       </c>
       <c r="Q33" s="12">
         <f t="shared" si="5"/>
-        <v>0.91898845741878621</v>
+        <v>0.91899095419170718</v>
       </c>
       <c r="R33" s="5">
         <v>331018</v>
@@ -5994,14 +5994,14 @@
       </c>
       <c r="T33" s="11">
         <f t="shared" si="6"/>
-        <v>34435</v>
+        <v>34438</v>
       </c>
       <c r="U33" s="6">
-        <v>231867</v>
+        <v>231870</v>
       </c>
       <c r="V33" s="12">
         <f t="shared" si="7"/>
-        <v>0.70046643989148627</v>
+        <v>0.70047550284274573</v>
       </c>
       <c r="W33" s="5">
         <v>322207</v>
@@ -6011,14 +6011,14 @@
       </c>
       <c r="Y33" s="11">
         <f t="shared" si="8"/>
-        <v>46985</v>
+        <v>46988</v>
       </c>
       <c r="Z33" s="6">
-        <v>233029</v>
+        <v>233032</v>
       </c>
       <c r="AA33" s="12">
         <f t="shared" si="9"/>
-        <v>0.72322761454592854</v>
+        <v>0.72323692533061046</v>
       </c>
       <c r="AB33" s="5">
         <v>823883</v>
@@ -6028,14 +6028,14 @@
       </c>
       <c r="AD33" s="11">
         <f t="shared" si="10"/>
-        <v>298885</v>
+        <v>298886</v>
       </c>
       <c r="AE33" s="6">
-        <v>758710</v>
+        <v>758711</v>
       </c>
       <c r="AF33" s="12">
         <f t="shared" si="11"/>
-        <v>0.92089532130168972</v>
+        <v>0.92089653506626545</v>
       </c>
       <c r="AG33" s="5">
         <v>309633</v>
@@ -6045,14 +6045,14 @@
       </c>
       <c r="AI33" s="11">
         <f t="shared" si="12"/>
-        <v>165956</v>
+        <v>165958</v>
       </c>
       <c r="AJ33" s="6">
-        <v>235469</v>
+        <v>235471</v>
       </c>
       <c r="AK33" s="12">
         <f t="shared" si="13"/>
-        <v>0.76047772685727943</v>
+        <v>0.76048418611711288</v>
       </c>
       <c r="AL33" s="5">
         <v>305879</v>
@@ -6062,14 +6062,14 @@
       </c>
       <c r="AN33" s="11">
         <f t="shared" si="14"/>
-        <v>116957</v>
+        <v>116959</v>
       </c>
       <c r="AO33" s="6">
-        <v>235824</v>
+        <v>235826</v>
       </c>
       <c r="AP33" s="12">
         <f t="shared" si="15"/>
-        <v>0.77097152795713342</v>
+        <v>0.77097806649034417</v>
       </c>
       <c r="AQ33" s="5">
         <v>838229</v>
@@ -6079,14 +6079,14 @@
       </c>
       <c r="AS33" s="11">
         <f t="shared" si="16"/>
-        <v>575966</v>
+        <v>575970</v>
       </c>
       <c r="AT33" s="6">
-        <v>775911</v>
+        <v>775915</v>
       </c>
       <c r="AU33" s="12">
         <f t="shared" si="17"/>
-        <v>0.92565516105980583</v>
+        <v>0.92565993302546201</v>
       </c>
       <c r="AV33" s="5">
         <v>298136</v>
@@ -6096,14 +6096,14 @@
       </c>
       <c r="AX33" s="11">
         <f t="shared" si="18"/>
-        <v>108174</v>
+        <v>108177</v>
       </c>
       <c r="AY33" s="6">
-        <v>237506</v>
+        <v>237509</v>
       </c>
       <c r="AZ33" s="12">
         <f t="shared" si="19"/>
-        <v>0.79663643437894116</v>
+        <v>0.7966464969007433</v>
       </c>
       <c r="BA33" s="5">
         <v>294597</v>
@@ -6113,14 +6113,14 @@
       </c>
       <c r="BC33" s="11">
         <f t="shared" si="20"/>
-        <v>112369</v>
+        <v>112372</v>
       </c>
       <c r="BD33" s="6">
-        <v>237897</v>
+        <v>237900</v>
       </c>
       <c r="BE33" s="12">
         <f t="shared" si="21"/>
-        <v>0.80753368160571903</v>
+        <v>0.80754386500880859</v>
       </c>
       <c r="BF33" s="5">
         <v>864165</v>
@@ -6130,14 +6130,14 @@
       </c>
       <c r="BH33" s="11">
         <f t="shared" si="22"/>
-        <v>636703</v>
+        <v>636710</v>
       </c>
       <c r="BI33" s="6">
-        <v>791668</v>
+        <v>791675</v>
       </c>
       <c r="BJ33" s="12">
         <f t="shared" si="23"/>
-        <v>0.91610745633067758</v>
+        <v>0.91611555663559618</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6579,14 +6579,14 @@
       </c>
       <c r="E36" s="11">
         <f t="shared" si="0"/>
-        <v>57015</v>
+        <v>57021</v>
       </c>
       <c r="F36" s="6">
-        <v>323162</v>
+        <v>323168</v>
       </c>
       <c r="G36" s="12">
         <f t="shared" si="1"/>
-        <v>0.58150691340430283</v>
+        <v>0.58151770997531183</v>
       </c>
       <c r="H36" s="5">
         <v>576385</v>
@@ -6596,14 +6596,14 @@
       </c>
       <c r="J36" s="11">
         <f t="shared" si="2"/>
-        <v>61334</v>
+        <v>61337</v>
       </c>
       <c r="K36" s="6">
-        <v>325773</v>
+        <v>325776</v>
       </c>
       <c r="L36" s="12">
         <f t="shared" si="3"/>
-        <v>0.56520034352039006</v>
+        <v>0.56520554837478421</v>
       </c>
       <c r="M36" s="5">
         <v>1291465</v>
@@ -6613,14 +6613,14 @@
       </c>
       <c r="O36" s="11">
         <f t="shared" si="4"/>
-        <v>325476</v>
+        <v>325479</v>
       </c>
       <c r="P36" s="6">
-        <v>1125068</v>
+        <v>1125071</v>
       </c>
       <c r="Q36" s="12">
         <f t="shared" si="5"/>
-        <v>0.87115639990243643</v>
+        <v>0.87115872284576046</v>
       </c>
       <c r="R36" s="5">
         <v>567427</v>
@@ -6630,14 +6630,14 @@
       </c>
       <c r="T36" s="11">
         <f t="shared" si="6"/>
-        <v>80875</v>
+        <v>80878</v>
       </c>
       <c r="U36" s="6">
-        <v>330320</v>
+        <v>330323</v>
       </c>
       <c r="V36" s="12">
         <f t="shared" si="7"/>
-        <v>0.58213655677294174</v>
+        <v>0.58214184379664702</v>
       </c>
       <c r="W36" s="5">
         <v>554725</v>
@@ -6647,14 +6647,14 @@
       </c>
       <c r="Y36" s="11">
         <f t="shared" si="8"/>
-        <v>102843</v>
+        <v>102847</v>
       </c>
       <c r="Z36" s="6">
-        <v>331911</v>
+        <v>331915</v>
       </c>
       <c r="AA36" s="12">
         <f t="shared" si="9"/>
-        <v>0.59833430979314073</v>
+        <v>0.59834152057325707</v>
       </c>
       <c r="AB36" s="5">
         <v>1322160</v>
@@ -6664,14 +6664,14 @@
       </c>
       <c r="AD36" s="11">
         <f t="shared" si="10"/>
-        <v>585411</v>
+        <v>585414</v>
       </c>
       <c r="AE36" s="6">
-        <v>1156227</v>
+        <v>1156230</v>
       </c>
       <c r="AF36" s="12">
         <f t="shared" si="11"/>
-        <v>0.87449854783082226</v>
+        <v>0.87450081684516245</v>
       </c>
       <c r="AG36" s="5">
         <v>528657</v>
@@ -6681,14 +6681,14 @@
       </c>
       <c r="AI36" s="11">
         <f t="shared" si="12"/>
-        <v>239158</v>
+        <v>239162</v>
       </c>
       <c r="AJ36" s="6">
-        <v>336438</v>
+        <v>336442</v>
       </c>
       <c r="AK36" s="12">
         <f t="shared" si="13"/>
-        <v>0.63640129611449392</v>
+        <v>0.63640886245713191</v>
       </c>
       <c r="AL36" s="5">
         <v>520551</v>
@@ -6698,14 +6698,14 @@
       </c>
       <c r="AN36" s="11">
         <f t="shared" si="14"/>
-        <v>188254</v>
+        <v>188258</v>
       </c>
       <c r="AO36" s="6">
-        <v>336830</v>
+        <v>336834</v>
       </c>
       <c r="AP36" s="12">
         <f t="shared" si="15"/>
-        <v>0.64706436064862038</v>
+        <v>0.64707204481405278</v>
       </c>
       <c r="AQ36" s="5">
         <v>1349417</v>
@@ -6715,14 +6715,14 @@
       </c>
       <c r="AS36" s="11">
         <f t="shared" si="16"/>
-        <v>963179</v>
+        <v>963182</v>
       </c>
       <c r="AT36" s="6">
-        <v>1181476</v>
+        <v>1181479</v>
       </c>
       <c r="AU36" s="12">
         <f t="shared" si="17"/>
-        <v>0.87554551335873199</v>
+        <v>0.87554773654103957</v>
       </c>
       <c r="AV36" s="5">
         <v>479560</v>
@@ -6732,14 +6732,14 @@
       </c>
       <c r="AX36" s="11">
         <f t="shared" si="18"/>
-        <v>182776</v>
+        <v>182780</v>
       </c>
       <c r="AY36" s="6">
-        <v>340655</v>
+        <v>340659</v>
       </c>
       <c r="AZ36" s="12">
         <f t="shared" si="19"/>
-        <v>0.71034906998081571</v>
+        <v>0.71035741096004668</v>
       </c>
       <c r="BA36" s="5">
         <v>474262</v>
@@ -6749,14 +6749,14 @@
       </c>
       <c r="BC36" s="11">
         <f t="shared" si="20"/>
-        <v>186137</v>
+        <v>186140</v>
       </c>
       <c r="BD36" s="6">
-        <v>341581</v>
+        <v>341584</v>
       </c>
       <c r="BE36" s="12">
         <f t="shared" si="21"/>
-        <v>0.72023691546023083</v>
+        <v>0.72024324107771653</v>
       </c>
       <c r="BF36" s="5">
         <v>1384075</v>
@@ -6766,14 +6766,14 @@
       </c>
       <c r="BH36" s="11">
         <f t="shared" si="22"/>
-        <v>1004969</v>
+        <v>1004976</v>
       </c>
       <c r="BI36" s="6">
-        <v>1200548</v>
+        <v>1200555</v>
       </c>
       <c r="BJ36" s="12">
         <f t="shared" si="23"/>
-        <v>0.86740097176814845</v>
+        <v>0.86740602929754529</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6791,14 +6791,14 @@
       </c>
       <c r="E37" s="11">
         <f t="shared" si="0"/>
-        <v>66185</v>
+        <v>66187</v>
       </c>
       <c r="F37" s="6">
-        <v>318009</v>
+        <v>318011</v>
       </c>
       <c r="G37" s="12">
         <f t="shared" si="1"/>
-        <v>0.74983199994341054</v>
+        <v>0.74983671573447264</v>
       </c>
       <c r="H37" s="5">
         <v>438161</v>
@@ -6808,14 +6808,14 @@
       </c>
       <c r="J37" s="11">
         <f t="shared" si="2"/>
-        <v>71265</v>
+        <v>71267</v>
       </c>
       <c r="K37" s="6">
-        <v>321984</v>
+        <v>321986</v>
       </c>
       <c r="L37" s="12">
         <f t="shared" si="3"/>
-        <v>0.73485317040996345</v>
+        <v>0.73485773494217876</v>
       </c>
       <c r="M37" s="5">
         <v>650458</v>
@@ -6825,14 +6825,14 @@
       </c>
       <c r="O37" s="11">
         <f t="shared" si="4"/>
-        <v>156084</v>
+        <v>156086</v>
       </c>
       <c r="P37" s="6">
-        <v>542399</v>
+        <v>542401</v>
       </c>
       <c r="Q37" s="12">
         <f t="shared" si="5"/>
-        <v>0.8338724406495116</v>
+        <v>0.83387551540606775</v>
       </c>
       <c r="R37" s="5">
         <v>451955</v>
@@ -6842,14 +6842,14 @@
       </c>
       <c r="T37" s="11">
         <f t="shared" si="6"/>
-        <v>89274</v>
+        <v>89277</v>
       </c>
       <c r="U37" s="6">
-        <v>330067</v>
+        <v>330070</v>
       </c>
       <c r="V37" s="12">
         <f t="shared" si="7"/>
-        <v>0.73030943346129595</v>
+        <v>0.73031607129028331</v>
       </c>
       <c r="W37" s="5">
         <v>454656</v>
@@ -6859,14 +6859,14 @@
       </c>
       <c r="Y37" s="11">
         <f t="shared" si="8"/>
-        <v>110097</v>
+        <v>110100</v>
       </c>
       <c r="Z37" s="6">
-        <v>333662</v>
+        <v>333665</v>
       </c>
       <c r="AA37" s="12">
         <f t="shared" si="9"/>
-        <v>0.73387792088963966</v>
+        <v>0.73388451928490994</v>
       </c>
       <c r="AB37" s="5">
         <v>682420</v>
@@ -6876,14 +6876,14 @@
       </c>
       <c r="AD37" s="11">
         <f t="shared" si="10"/>
-        <v>263214</v>
+        <v>263216</v>
       </c>
       <c r="AE37" s="6">
-        <v>566120</v>
+        <v>566122</v>
       </c>
       <c r="AF37" s="12">
         <f t="shared" si="11"/>
-        <v>0.82957709328565987</v>
+        <v>0.82958002403212094</v>
       </c>
       <c r="AG37" s="5">
         <v>455096</v>
@@ -6893,14 +6893,14 @@
       </c>
       <c r="AI37" s="11">
         <f t="shared" si="12"/>
-        <v>253297</v>
+        <v>253300</v>
       </c>
       <c r="AJ37" s="6">
-        <v>341049</v>
+        <v>341052</v>
       </c>
       <c r="AK37" s="12">
         <f t="shared" si="13"/>
-        <v>0.74940012656670241</v>
+        <v>0.74940671858245289</v>
       </c>
       <c r="AL37" s="5">
         <v>455153</v>
@@ -6910,14 +6910,14 @@
       </c>
       <c r="AN37" s="11">
         <f t="shared" si="14"/>
-        <v>230820</v>
+        <v>230824</v>
       </c>
       <c r="AO37" s="6">
-        <v>342560</v>
+        <v>342564</v>
       </c>
       <c r="AP37" s="12">
         <f t="shared" si="15"/>
-        <v>0.75262604003488942</v>
+        <v>0.75263482828850958</v>
       </c>
       <c r="AQ37" s="5">
         <v>700400</v>
@@ -6927,14 +6927,14 @@
       </c>
       <c r="AS37" s="11">
         <f t="shared" si="16"/>
-        <v>433751</v>
+        <v>433759</v>
       </c>
       <c r="AT37" s="6">
-        <v>584996</v>
+        <v>585004</v>
       </c>
       <c r="AU37" s="12">
         <f t="shared" si="17"/>
-        <v>0.83523129640205596</v>
+        <v>0.83524271844660192</v>
       </c>
       <c r="AV37" s="5">
         <v>439004</v>
@@ -6944,14 +6944,14 @@
       </c>
       <c r="AX37" s="11">
         <f t="shared" si="18"/>
-        <v>227687</v>
+        <v>227691</v>
       </c>
       <c r="AY37" s="6">
-        <v>349517</v>
+        <v>349521</v>
       </c>
       <c r="AZ37" s="12">
         <f t="shared" si="19"/>
-        <v>0.7961590327195196</v>
+        <v>0.79616814425381088</v>
       </c>
       <c r="BA37" s="5">
         <v>433985</v>
@@ -6961,14 +6961,14 @@
       </c>
       <c r="BC37" s="11">
         <f t="shared" si="20"/>
-        <v>235066</v>
+        <v>235071</v>
       </c>
       <c r="BD37" s="6">
-        <v>351520</v>
+        <v>351525</v>
       </c>
       <c r="BE37" s="12">
         <f t="shared" si="21"/>
-        <v>0.80998191181722867</v>
+        <v>0.80999343295275184</v>
       </c>
       <c r="BF37" s="5">
         <v>706472</v>
@@ -6978,14 +6978,14 @@
       </c>
       <c r="BH37" s="11">
         <f t="shared" si="22"/>
-        <v>460605</v>
+        <v>460613</v>
       </c>
       <c r="BI37" s="6">
-        <v>599337</v>
+        <v>599345</v>
       </c>
       <c r="BJ37" s="12">
         <f t="shared" si="23"/>
-        <v>0.84835209321813176</v>
+        <v>0.8483634170922556</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7427,14 +7427,14 @@
       </c>
       <c r="E40" s="11">
         <f t="shared" si="0"/>
-        <v>26504</v>
+        <v>26506</v>
       </c>
       <c r="F40" s="6">
-        <v>135023</v>
+        <v>135025</v>
       </c>
       <c r="G40" s="12">
         <f t="shared" si="1"/>
-        <v>0.82124784079020996</v>
+        <v>0.8212600053524074</v>
       </c>
       <c r="H40" s="5">
         <v>169073</v>
@@ -7444,14 +7444,14 @@
       </c>
       <c r="J40" s="11">
         <f t="shared" si="2"/>
-        <v>29027</v>
+        <v>29029</v>
       </c>
       <c r="K40" s="6">
-        <v>136944</v>
+        <v>136946</v>
       </c>
       <c r="L40" s="12">
         <f t="shared" si="3"/>
-        <v>0.80996965807668875</v>
+        <v>0.80998148728655672</v>
       </c>
       <c r="M40" s="5">
         <v>263762</v>
@@ -7461,14 +7461,14 @@
       </c>
       <c r="O40" s="11">
         <f t="shared" si="4"/>
-        <v>67955</v>
+        <v>67957</v>
       </c>
       <c r="P40" s="6">
-        <v>241232</v>
+        <v>241234</v>
       </c>
       <c r="Q40" s="12">
         <f t="shared" si="5"/>
-        <v>0.91458208536483643</v>
+        <v>0.91458966795823504</v>
       </c>
       <c r="R40" s="5">
         <v>173127</v>
@@ -7478,14 +7478,14 @@
       </c>
       <c r="T40" s="11">
         <f t="shared" si="6"/>
-        <v>40605</v>
+        <v>40608</v>
       </c>
       <c r="U40" s="6">
-        <v>139965</v>
+        <v>139968</v>
       </c>
       <c r="V40" s="12">
         <f t="shared" si="7"/>
-        <v>0.80845275433641195</v>
+        <v>0.80847008265608489</v>
       </c>
       <c r="W40" s="5">
         <v>173204</v>
@@ -7495,14 +7495,14 @@
       </c>
       <c r="Y40" s="11">
         <f t="shared" si="8"/>
-        <v>53699</v>
+        <v>53703</v>
       </c>
       <c r="Z40" s="6">
-        <v>140989</v>
+        <v>140993</v>
       </c>
       <c r="AA40" s="12">
         <f t="shared" si="9"/>
-        <v>0.81400545022054915</v>
+        <v>0.81402854437541861</v>
       </c>
       <c r="AB40" s="5">
         <v>273181</v>
@@ -7512,14 +7512,14 @@
       </c>
       <c r="AD40" s="11">
         <f t="shared" si="10"/>
-        <v>145551</v>
+        <v>145554</v>
       </c>
       <c r="AE40" s="6">
-        <v>249072</v>
+        <v>249075</v>
       </c>
       <c r="AF40" s="12">
         <f t="shared" si="11"/>
-        <v>0.91174715664705819</v>
+        <v>0.91175813837711994</v>
       </c>
       <c r="AG40" s="5">
         <v>172895</v>
@@ -7529,14 +7529,14 @@
       </c>
       <c r="AI40" s="11">
         <f t="shared" si="12"/>
-        <v>112319</v>
+        <v>112324</v>
       </c>
       <c r="AJ40" s="6">
-        <v>143495</v>
+        <v>143500</v>
       </c>
       <c r="AK40" s="12">
         <f t="shared" si="13"/>
-        <v>0.82995459672055294</v>
+        <v>0.82998351600682496</v>
       </c>
       <c r="AL40" s="5">
         <v>173328</v>
@@ -7546,14 +7546,14 @@
       </c>
       <c r="AN40" s="11">
         <f t="shared" si="14"/>
-        <v>107535</v>
+        <v>107539</v>
       </c>
       <c r="AO40" s="6">
-        <v>144481</v>
+        <v>144485</v>
       </c>
       <c r="AP40" s="12">
         <f t="shared" si="15"/>
-        <v>0.83356987907320224</v>
+        <v>0.83359295670636024</v>
       </c>
       <c r="AQ40" s="5">
         <v>281909</v>
@@ -7563,14 +7563,14 @@
       </c>
       <c r="AS40" s="11">
         <f t="shared" si="16"/>
-        <v>206382</v>
+        <v>206384</v>
       </c>
       <c r="AT40" s="6">
-        <v>255769</v>
+        <v>255771</v>
       </c>
       <c r="AU40" s="12">
         <f t="shared" si="17"/>
-        <v>0.90727504265560877</v>
+        <v>0.90728213714354633</v>
       </c>
       <c r="AV40" s="5">
         <v>172382</v>
@@ -7580,14 +7580,14 @@
       </c>
       <c r="AX40" s="11">
         <f t="shared" si="18"/>
-        <v>103191</v>
+        <v>103193</v>
       </c>
       <c r="AY40" s="6">
-        <v>146400</v>
+        <v>146402</v>
       </c>
       <c r="AZ40" s="12">
         <f t="shared" si="19"/>
-        <v>0.84927660660625814</v>
+        <v>0.84928820874569266</v>
       </c>
       <c r="BA40" s="5">
         <v>172548</v>
@@ -7597,14 +7597,14 @@
       </c>
       <c r="BC40" s="11">
         <f t="shared" si="20"/>
-        <v>105622</v>
+        <v>105624</v>
       </c>
       <c r="BD40" s="6">
-        <v>146858</v>
+        <v>146860</v>
       </c>
       <c r="BE40" s="12">
         <f t="shared" si="21"/>
-        <v>0.85111389294573103</v>
+        <v>0.85112548392331411</v>
       </c>
       <c r="BF40" s="5">
         <v>291194</v>
@@ -7614,14 +7614,14 @@
       </c>
       <c r="BH40" s="11">
         <f t="shared" si="22"/>
-        <v>208601</v>
+        <v>208603</v>
       </c>
       <c r="BI40" s="6">
-        <v>260563</v>
+        <v>260565</v>
       </c>
       <c r="BJ40" s="12">
         <f t="shared" si="23"/>
-        <v>0.89480895897580304</v>
+        <v>0.89481582724918785</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7639,14 +7639,14 @@
       </c>
       <c r="E41" s="11">
         <f t="shared" si="0"/>
-        <v>77334</v>
+        <v>77347</v>
       </c>
       <c r="F41" s="6">
-        <v>452086</v>
+        <v>452099</v>
       </c>
       <c r="G41" s="12">
         <f t="shared" si="1"/>
-        <v>0.73712598380261829</v>
+        <v>0.73714718029574</v>
       </c>
       <c r="H41" s="5">
         <v>630477</v>
@@ -7656,14 +7656,14 @@
       </c>
       <c r="J41" s="11">
         <f t="shared" si="2"/>
-        <v>82477</v>
+        <v>82493</v>
       </c>
       <c r="K41" s="6">
-        <v>458546</v>
+        <v>458562</v>
       </c>
       <c r="L41" s="12">
         <f t="shared" si="3"/>
-        <v>0.72730012355724316</v>
+        <v>0.72732550116816319</v>
       </c>
       <c r="M41" s="5">
         <v>852643</v>
@@ -7673,14 +7673,14 @@
       </c>
       <c r="O41" s="11">
         <f t="shared" si="4"/>
-        <v>165711</v>
+        <v>165727</v>
       </c>
       <c r="P41" s="6">
-        <v>685229</v>
+        <v>685245</v>
       </c>
       <c r="Q41" s="12">
         <f t="shared" si="5"/>
-        <v>0.8036528769954131</v>
+        <v>0.80367164217615106</v>
       </c>
       <c r="R41" s="5">
         <v>651946</v>
@@ -7690,14 +7690,14 @@
       </c>
       <c r="T41" s="11">
         <f t="shared" si="6"/>
-        <v>104734</v>
+        <v>104744</v>
       </c>
       <c r="U41" s="6">
-        <v>468856</v>
+        <v>468866</v>
       </c>
       <c r="V41" s="12">
         <f t="shared" si="7"/>
-        <v>0.71916385712927144</v>
+        <v>0.71917919582296697</v>
       </c>
       <c r="W41" s="5">
         <v>654087</v>
@@ -7707,14 +7707,14 @@
       </c>
       <c r="Y41" s="11">
         <f t="shared" si="8"/>
-        <v>129275</v>
+        <v>129286</v>
       </c>
       <c r="Z41" s="6">
-        <v>472902</v>
+        <v>472913</v>
       </c>
       <c r="AA41" s="12">
         <f t="shared" si="9"/>
-        <v>0.72299556481018579</v>
+        <v>0.72301238214488284</v>
       </c>
       <c r="AB41" s="5">
         <v>882248</v>
@@ -7724,14 +7724,14 @@
       </c>
       <c r="AD41" s="11">
         <f t="shared" si="10"/>
-        <v>296903</v>
+        <v>296916</v>
       </c>
       <c r="AE41" s="6">
-        <v>708751</v>
+        <v>708764</v>
       </c>
       <c r="AF41" s="12">
         <f t="shared" si="11"/>
-        <v>0.80334667803157389</v>
+        <v>0.80336141311740006</v>
       </c>
       <c r="AG41" s="5">
         <v>638043</v>
@@ -7741,14 +7741,14 @@
       </c>
       <c r="AI41" s="11">
         <f t="shared" si="12"/>
-        <v>359889</v>
+        <v>359901</v>
       </c>
       <c r="AJ41" s="6">
-        <v>481416</v>
+        <v>481428</v>
       </c>
       <c r="AK41" s="12">
         <f t="shared" si="13"/>
-        <v>0.7545196797081074</v>
+        <v>0.75453848721794614</v>
       </c>
       <c r="AL41" s="5">
         <v>632207</v>
@@ -7758,14 +7758,14 @@
       </c>
       <c r="AN41" s="11">
         <f t="shared" si="14"/>
-        <v>319939</v>
+        <v>319954</v>
       </c>
       <c r="AO41" s="6">
-        <v>483044</v>
+        <v>483059</v>
       </c>
       <c r="AP41" s="12">
         <f t="shared" si="15"/>
-        <v>0.76405987279482823</v>
+        <v>0.76408359920089464</v>
       </c>
       <c r="AQ41" s="5">
         <v>865402</v>
@@ -7775,14 +7775,14 @@
       </c>
       <c r="AS41" s="11">
         <f t="shared" si="16"/>
-        <v>516860</v>
+        <v>516890</v>
       </c>
       <c r="AT41" s="6">
-        <v>724233</v>
+        <v>724263</v>
       </c>
       <c r="AU41" s="12">
         <f t="shared" si="17"/>
-        <v>0.83687465478471279</v>
+        <v>0.83690932075497859</v>
       </c>
       <c r="AV41" s="5">
         <v>609881</v>
@@ -7792,14 +7792,14 @@
       </c>
       <c r="AX41" s="11">
         <f t="shared" si="18"/>
-        <v>321790</v>
+        <v>321806</v>
       </c>
       <c r="AY41" s="6">
-        <v>489985</v>
+        <v>490001</v>
       </c>
       <c r="AZ41" s="12">
         <f t="shared" si="19"/>
-        <v>0.80341082932572094</v>
+        <v>0.80343706395182013</v>
       </c>
       <c r="BA41" s="5">
         <v>594974</v>
@@ -7809,14 +7809,14 @@
       </c>
       <c r="BC41" s="11">
         <f t="shared" si="20"/>
-        <v>336348</v>
+        <v>336364</v>
       </c>
       <c r="BD41" s="6">
-        <v>492357</v>
+        <v>492373</v>
       </c>
       <c r="BE41" s="12">
         <f t="shared" si="21"/>
-        <v>0.82752691714259785</v>
+        <v>0.82755380907400999</v>
       </c>
       <c r="BF41" s="5">
         <v>867754</v>
@@ -7826,14 +7826,14 @@
       </c>
       <c r="BH41" s="11">
         <f t="shared" si="22"/>
-        <v>556594</v>
+        <v>556618</v>
       </c>
       <c r="BI41" s="6">
-        <v>737706</v>
+        <v>737730</v>
       </c>
       <c r="BJ41" s="12">
         <f t="shared" si="23"/>
-        <v>0.85013264127851906</v>
+        <v>0.85016029888655076</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -8360,14 +8360,14 @@
       </c>
       <c r="AD44" s="11">
         <f t="shared" si="10"/>
-        <v>127295</v>
+        <v>127297</v>
       </c>
       <c r="AE44" s="6">
-        <v>244440</v>
+        <v>244442</v>
       </c>
       <c r="AF44" s="12">
         <f t="shared" si="11"/>
-        <v>0.81977329130055676</v>
+        <v>0.81977999865852835</v>
       </c>
       <c r="AG44" s="5">
         <v>213000</v>
@@ -8411,14 +8411,14 @@
       </c>
       <c r="AS44" s="11">
         <f t="shared" si="16"/>
-        <v>186779</v>
+        <v>186780</v>
       </c>
       <c r="AT44" s="6">
-        <v>252329</v>
+        <v>252330</v>
       </c>
       <c r="AU44" s="12">
         <f t="shared" si="17"/>
-        <v>0.8254732103716983</v>
+        <v>0.82547648178802535</v>
       </c>
       <c r="AV44" s="5">
         <v>207845</v>
@@ -8462,14 +8462,14 @@
       </c>
       <c r="BH44" s="11">
         <f t="shared" si="22"/>
-        <v>207907</v>
+        <v>207908</v>
       </c>
       <c r="BI44" s="6">
-        <v>257930</v>
+        <v>257931</v>
       </c>
       <c r="BJ44" s="12">
         <f t="shared" si="23"/>
-        <v>0.80738614487436733</v>
+        <v>0.80738927512732306</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8521,14 +8521,14 @@
       </c>
       <c r="O45" s="11">
         <f t="shared" si="4"/>
-        <v>53664</v>
+        <v>53667</v>
       </c>
       <c r="P45" s="6">
-        <v>209803</v>
+        <v>209806</v>
       </c>
       <c r="Q45" s="12">
         <f t="shared" si="5"/>
-        <v>0.83065295198276956</v>
+        <v>0.83066482959584442</v>
       </c>
       <c r="R45" s="5">
         <v>182214</v>
@@ -8538,14 +8538,14 @@
       </c>
       <c r="T45" s="11">
         <f t="shared" si="6"/>
-        <v>32048</v>
+        <v>32049</v>
       </c>
       <c r="U45" s="6">
-        <v>137699</v>
+        <v>137700</v>
       </c>
       <c r="V45" s="12">
         <f t="shared" si="7"/>
-        <v>0.75569934253130933</v>
+        <v>0.75570483058381899</v>
       </c>
       <c r="W45" s="5">
         <v>179895</v>
@@ -8555,14 +8555,14 @@
       </c>
       <c r="Y45" s="11">
         <f t="shared" si="8"/>
-        <v>43452</v>
+        <v>43453</v>
       </c>
       <c r="Z45" s="6">
-        <v>139031</v>
+        <v>139032</v>
       </c>
       <c r="AA45" s="12">
         <f t="shared" si="9"/>
-        <v>0.7728452708524417</v>
+        <v>0.77285082965062957</v>
       </c>
       <c r="AB45" s="5">
         <v>256988</v>
@@ -8572,14 +8572,14 @@
       </c>
       <c r="AD45" s="11">
         <f t="shared" si="10"/>
-        <v>108358</v>
+        <v>108359</v>
       </c>
       <c r="AE45" s="6">
-        <v>218424</v>
+        <v>218425</v>
       </c>
       <c r="AF45" s="12">
         <f t="shared" si="11"/>
-        <v>0.84993851853004809</v>
+        <v>0.84994240976232349</v>
       </c>
       <c r="AG45" s="5">
         <v>177277</v>
@@ -8589,14 +8589,14 @@
       </c>
       <c r="AI45" s="11">
         <f t="shared" si="12"/>
-        <v>104877</v>
+        <v>104878</v>
       </c>
       <c r="AJ45" s="6">
-        <v>142407</v>
+        <v>142408</v>
       </c>
       <c r="AK45" s="12">
         <f t="shared" si="13"/>
-        <v>0.80330217681932792</v>
+        <v>0.80330781770900905</v>
       </c>
       <c r="AL45" s="5">
         <v>180013</v>
@@ -8657,14 +8657,14 @@
       </c>
       <c r="BC45" s="11">
         <f t="shared" si="20"/>
-        <v>101506</v>
+        <v>101507</v>
       </c>
       <c r="BD45" s="6">
-        <v>147935</v>
+        <v>147936</v>
       </c>
       <c r="BE45" s="12">
         <f t="shared" si="21"/>
-        <v>0.81346882440598933</v>
+        <v>0.81347432323198998</v>
       </c>
       <c r="BF45" s="5">
         <v>279089</v>
@@ -9099,15 +9099,15 @@
       </c>
       <c r="E48" s="13">
         <f t="shared" si="0"/>
-        <v>546935</v>
+        <v>546965</v>
       </c>
       <c r="F48" s="15">
         <f>SUM(F10:F47)</f>
-        <v>3051638</v>
+        <v>3051668</v>
       </c>
       <c r="G48" s="14">
         <f t="shared" si="1"/>
-        <v>0.67869740471977502</v>
+        <v>0.67870407684869127</v>
       </c>
       <c r="H48" s="15">
         <f>SUM(H10:H47)</f>
@@ -9119,15 +9119,15 @@
       </c>
       <c r="J48" s="13">
         <f t="shared" si="2"/>
-        <v>589333</v>
+        <v>589363</v>
       </c>
       <c r="K48" s="15">
         <f>SUM(K10:K47)</f>
-        <v>3089650</v>
+        <v>3089680</v>
       </c>
       <c r="L48" s="14">
         <f t="shared" si="3"/>
-        <v>0.65985099346588083</v>
+        <v>0.65985740051192299</v>
       </c>
       <c r="M48" s="15">
         <f>SUM(M10:M47)</f>
@@ -9139,15 +9139,15 @@
       </c>
       <c r="O48" s="13">
         <f t="shared" si="4"/>
-        <v>2192378</v>
+        <v>2192420</v>
       </c>
       <c r="P48" s="15">
         <f>SUM(P10:P47)</f>
-        <v>8045029</v>
+        <v>8045071</v>
       </c>
       <c r="Q48" s="14">
         <f t="shared" si="5"/>
-        <v>0.86350535757794333</v>
+        <v>0.86350986560706511</v>
       </c>
       <c r="R48" s="15">
         <f>SUM(R10:R47)</f>
@@ -9159,15 +9159,15 @@
       </c>
       <c r="T48" s="13">
         <f t="shared" si="6"/>
-        <v>772951</v>
+        <v>772980</v>
       </c>
       <c r="U48" s="15">
         <f>SUM(U10:U47)</f>
-        <v>3153591</v>
+        <v>3153620</v>
       </c>
       <c r="V48" s="14">
         <f t="shared" si="7"/>
-        <v>0.66035133404500268</v>
+        <v>0.66035740654733011</v>
       </c>
       <c r="W48" s="15">
         <f>SUM(W10:W47)</f>
@@ -9179,15 +9179,15 @@
       </c>
       <c r="Y48" s="13">
         <f t="shared" si="8"/>
-        <v>978304</v>
+        <v>978337</v>
       </c>
       <c r="Z48" s="15">
         <f>SUM(Z10:Z47)</f>
-        <v>3178257</v>
+        <v>3178290</v>
       </c>
       <c r="AA48" s="14">
         <f t="shared" si="9"/>
-        <v>0.67237789066851761</v>
+        <v>0.672384872001491</v>
       </c>
       <c r="AB48" s="15">
         <f>SUM(AB10:AB47)</f>
@@ -9199,15 +9199,15 @@
       </c>
       <c r="AD48" s="13">
         <f t="shared" si="10"/>
-        <v>3988083</v>
+        <v>3988120</v>
       </c>
       <c r="AE48" s="15">
         <f>SUM(AE10:AE47)</f>
-        <v>8342263</v>
+        <v>8342300</v>
       </c>
       <c r="AF48" s="14">
         <f t="shared" si="11"/>
-        <v>0.86383520175901207</v>
+        <v>0.86383903308181564</v>
       </c>
       <c r="AG48" s="15">
         <f>SUM(AG10:AG47)</f>
@@ -9219,15 +9219,15 @@
       </c>
       <c r="AI48" s="13">
         <f t="shared" si="12"/>
-        <v>2361890</v>
+        <v>2361923</v>
       </c>
       <c r="AJ48" s="15">
         <f>SUM(AJ10:AJ47)</f>
-        <v>3233232</v>
+        <v>3233265</v>
       </c>
       <c r="AK48" s="14">
         <f t="shared" si="13"/>
-        <v>0.70143644222600388</v>
+        <v>0.70144360144086793</v>
       </c>
       <c r="AL48" s="15">
         <f>SUM(AL10:AL47)</f>
@@ -9239,15 +9239,15 @@
       </c>
       <c r="AN48" s="13">
         <f t="shared" si="14"/>
-        <v>2046854</v>
+        <v>2046890</v>
       </c>
       <c r="AO48" s="15">
         <f>SUM(AO10:AO47)</f>
-        <v>3245164</v>
+        <v>3245200</v>
       </c>
       <c r="AP48" s="14">
         <f t="shared" si="15"/>
-        <v>0.70977258242241337</v>
+        <v>0.70978045623494401</v>
       </c>
       <c r="AQ48" s="15">
         <f>SUM(AQ10:AQ47)</f>
@@ -9259,15 +9259,15 @@
       </c>
       <c r="AS48" s="13">
         <f t="shared" si="16"/>
-        <v>6760076</v>
+        <v>6760138</v>
       </c>
       <c r="AT48" s="15">
         <f>SUM(AT10:AT47)</f>
-        <v>8563009</v>
+        <v>8563071</v>
       </c>
       <c r="AU48" s="14">
         <f t="shared" si="17"/>
-        <v>0.8647759638788014</v>
+        <v>0.86478222524203952</v>
       </c>
       <c r="AV48" s="15">
         <f>SUM(AV10:AV47)</f>
@@ -9279,15 +9279,15 @@
       </c>
       <c r="AX48" s="13">
         <f t="shared" si="18"/>
-        <v>2013267</v>
+        <v>2013303</v>
       </c>
       <c r="AY48" s="15">
         <f>SUM(AY10:AY47)</f>
-        <v>3290804</v>
+        <v>3290840</v>
       </c>
       <c r="AZ48" s="14">
         <f t="shared" si="19"/>
-        <v>0.74412864265429379</v>
+        <v>0.74413678310603004</v>
       </c>
       <c r="BA48" s="15">
         <f>SUM(BA10:BA47)</f>
@@ -9299,15 +9299,15 @@
       </c>
       <c r="BC48" s="13">
         <f t="shared" si="20"/>
-        <v>2072292</v>
+        <v>2072332</v>
       </c>
       <c r="BD48" s="15">
         <f>SUM(BD10:BD47)</f>
-        <v>3302289</v>
+        <v>3302329</v>
       </c>
       <c r="BE48" s="14">
         <f t="shared" si="21"/>
-        <v>0.75712025098793023</v>
+        <v>0.75712942184185594</v>
       </c>
       <c r="BF48" s="15">
         <f>SUM(BF10:BF47)</f>
@@ -9319,15 +9319,15 @@
       </c>
       <c r="BH48" s="13">
         <f t="shared" si="22"/>
-        <v>7183759</v>
+        <v>7183826</v>
       </c>
       <c r="BI48" s="15">
         <f>SUM(BI10:BI47)</f>
-        <v>8731229</v>
+        <v>8731296</v>
       </c>
       <c r="BJ48" s="14">
         <f t="shared" si="23"/>
-        <v>0.85810789959447575</v>
+        <v>0.85811448437529791</v>
       </c>
     </row>
     <row r="49" spans="1:62" x14ac:dyDescent="0.3">
